--- a/www/download/COUNTRY.CYP.rpPE.xlsx
+++ b/www/download/COUNTRY.CYP.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Chipre</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.772678123777948</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.796685775755041</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.877292976582033</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.883384436593682</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.926586570603177</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.06079414511591</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.09817702407959</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.03987932720202</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.882706029234349</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.799673759926997</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.792091754634952</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.783471856320399</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.727151112510703</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.679902076410497</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948682306625</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.39174061865908</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.412627775671541</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.436207969850558</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.37159561346491</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.439161398534408</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.561586824039254</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0.564807756777151</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.436982699384403</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.207150608415376</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.0769674379395862</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.0806215457459314</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.0953705664074949</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.106844707099763</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>0.0934747679673964</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.0906821617257361</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.00554625174316103</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>-0.00232044240620144</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.00419923811562128</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>-0.0412988983706686</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>0.0135454597270417</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.0972736584401741</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.0527567403488989</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>-0.036899030705724</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>-0.183311023786331</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>-0.246053761564579</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>-0.242252210359535</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>-0.211617077973035</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>-0.193363825943425</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>-0.195678030184447</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>-0.205377960375564</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>556.844</t>
+          <t>-0.594325943473606</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>559.558</t>
+          <t>-0.590557760528378</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>565.864</t>
+          <t>-0.587368567254177</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>576.508</t>
+          <t>-0.62330057573908</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>590.902</t>
+          <t>-0.616417038966138</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>605.96</t>
+          <t>-0.591006231917676</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>626.986</t>
+          <t>-0.600978208955949</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>631.03</t>
+          <t>-0.631280209449725</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>652.422</t>
+          <t>-0.696508817033301</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>663.882</t>
+          <t>-0.687759947129847</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>679.879</t>
+          <t>-0.673407270789351</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>694.745</t>
+          <t>-0.657506527985732</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>715.064</t>
+          <t>-0.62622879896599</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>724.744</t>
+          <t>-0.625594823412838</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>725.571</t>
+          <t>-0.627078469557614</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>385.082</t>
+          <t>1987551370.0567</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>388.735</t>
+          <t>2081173384.83923</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>393.173</t>
+          <t>1900168638.14717</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>400.651</t>
+          <t>1975927869.99787</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>410.296</t>
+          <t>2198758922.16449</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>421.155</t>
+          <t>2314637158.83423</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>433.872</t>
+          <t>2510471010.29609</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>443.031</t>
+          <t>2586654523.13843</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>455.955</t>
+          <t>2461263108.45974</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>458.638</t>
+          <t>2449790208.47076</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>473.113</t>
+          <t>2197318714.56007</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>494.479</t>
+          <t>2198020050.8686</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>516.413</t>
+          <t>2099162811.8811</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>540.57</t>
+          <t>2595128867.42997</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>541.705</t>
+          <t>1879505589.56892</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>1379667722.88091</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>1380545262.37383</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1376115854.5808</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>1524835610.94901</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>1534477477.83965</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>1511116727.54682</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>1600865286.35889</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>1776703716.9046</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>2014680164.67523</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>2276546056.31934</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>2265994999.01491</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>2269965680.39367</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>2211777468.53703</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>2265156933.77188</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>2302875609.81806</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>6961102.82277343</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>6983491.39909955</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>6878903.20686608</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>6981106.89600111</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>8074971.04009227</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>8596088.41727452</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>8650364.47883897</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>7890622.22862225</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>6214899.86022658</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>5675074.04329671</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>4500208.88140428</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>4107945.76611029</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>3310736.6292159</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>3438979.82810509</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>2628942.48264791</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>3437.99281708527</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>3407.9247792947</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>3265.63122710536</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>3157.12034458516</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>3264.21323419882</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>3400.01829535563</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>3376.11212077335</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>3458.45012472932</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>3755.90425099119</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>4051.79029974529</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>4345.09506930324</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>4611.5859411883</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>5506.84260305064</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>5950.16445875924</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>5506.41200925739</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>53.42</t>
+          <t>6557.77695871151</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>6946.302019958</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>52.33</t>
+          <t>6204.9692826808</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.73</t>
+          <t>6121.58531117552</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>51.18</t>
+          <t>6896.30219335529</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>52.39</t>
+          <t>7062.95367545479</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>7389.53435471416</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>7817.0880303639</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>53.44</t>
+          <t>8623.5190411988</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>52.72</t>
+          <t>8916.466981714</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>8665.38569481299</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.28</t>
+          <t>9217.20362468142</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>51.92</t>
+          <t>10404.9505148037</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>14615.7350793648</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>53.29</t>
+          <t>9750.86580452689</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>0.0588801643209682</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>0.07378336039471</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>0.0741482408019929</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>0.00619927864842973</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>36.72</t>
+          <t>0.0642599005611448</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>0.164023774584693</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>0.152305936146141</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>0.0659920845788287</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>-0.118622969213534</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>-0.173785927062979</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>-0.169070236107786</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>-0.137299228435607</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>-0.107493159423523</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>38.32</t>
+          <t>-0.109581749840273</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>-0.116025846729601</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>1801.60642508965</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>1885.24202254569</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>1842.95376845835</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>1995.49941526408</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>1973.87655566176</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>1885.15426599401</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>1902.78882302786</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.51</t>
+          <t>2218.23423176032</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>2577.0655686432</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>2939.68158238706</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>2989.28895231551</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>3334.34051158918</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>3862.56328610428</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>4674.07128540555</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.772678123777948</t>
+          <t>6167.03619214899</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.796685775755041</t>
+          <t>6110.3066357845</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.877292976582033</t>
+          <t>6015.46207926514</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.883384436593682</t>
+          <t>6536.32104890404</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.926586570603177</t>
+          <t>6447.8435039314</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06079414511591</t>
+          <t>6252.03445406215</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.09817702407959</t>
+          <t>6449.90042852091</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.03987932720202</t>
+          <t>6951.11000353914</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.882706029234349</t>
+          <t>7663.29465452731</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.799673759926997</t>
+          <t>8311.59567842036</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.792091754634952</t>
+          <t>7928.60391537758</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.783471856320399</t>
+          <t>7666.21303746595</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.727151112510703</t>
+          <t>7162.49180225724</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902076410497</t>
+          <t>6935.56930119988</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948682306625</t>
+          <t>7077.06087835912</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>55912370.6493975</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>68735167.0851981</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-1467224.69569227</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>65505458.9121117</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>260103636.584534</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>250377778.231141</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>372482466.671509</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>260457646.021783</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>282716795.841115</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>292638098.367308</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>218430490.859225</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>203723866.020577</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>23456642.086269</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>380295423.890817</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>202159642.942995</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>60428406.2870827</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>93580498.7893316</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>30988603.1547954</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>78474373.8541621</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>262252770.057396</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>279670833.776256</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>384746109.368827</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>254024986.851397</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>312511850.393009</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>215066985.934439</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>22047734.5658456</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>84074121.9481523</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-53490672.6980809</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>286467709.561572</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>68094255.8536724</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-4516035.63768524</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-24845331.7041335</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>-32455827.8504877</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-12968914.9420504</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>-2149133.47286173</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-29293055.5451158</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-12263642.6973172</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>6432659.17038649</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-29795054.5518934</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>77571112.4328688</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>196382756.29338</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>119649744.072425</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>76947314.7843499</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>93827714.3292442</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134065387.089323</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>6530.15229651608</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>6561.14559241478</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>6461.49801005375</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>6576.84152442179</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>6862.18128632786</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>7277.51674405098</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>7432.25855133618</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>7409.82824280944</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6754.25188864908</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>6867.15731807343</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>6588.11297939958</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>6613.64790239889</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>6392.57292908752</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>6175.55748103591</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>6255.93889759056</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8537.24321002712</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8507.76597770561</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8348.54893491171</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8498.23509847232</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8795.80050122728</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9336.86018128403</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9604.54625901923</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9500.33912911226</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>8540.16611325712</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>8763.88700821705</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>8408.6552363277</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>8418.77135181155</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>8153.22998901808</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>7902.19041293508</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>7851.61242901029</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>1986.75605591144</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>2113.1513598131</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>2064.14002772178</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>2082.82920060218</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>2162.24533912994</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>2147.15485544231</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>2290.77504501028</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>2299.08485759001</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>2752.51981074515</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>3347.5841392997</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>3450.0903690429</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>3796.76966358804</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>4611.57890213568</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>5147.43092485272</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>4628.49509079995</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>419026674.93382</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>456107819.963058</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>418139419.852039</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>424441010.115921</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>484170744.224816</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>543051626.959846</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>596982012.747754</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>573790755.910402</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-18.33</t>
+          <t>544171804.195266</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-24.61</t>
+          <t>485890271.592389</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>336877326.58677</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-21.16</t>
+          <t>396008632.950909</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-19.34</t>
+          <t>427665893.309566</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>456505671.073016</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>296646292.390139</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-59.43</t>
+          <t>3903.81993369891</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-59.06</t>
+          <t>4188.43247851129</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-58.74</t>
+          <t>4019.55139186513</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-62.33</t>
+          <t>4033.88415550994</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-61.64</t>
+          <t>4092.21245558792</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-59.1</t>
+          <t>4242.13096642063</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-60.1</t>
+          <t>4402.20095822659</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-63.13</t>
+          <t>4735.10396469906</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-69.65</t>
+          <t>5495.71255800651</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-68.78</t>
+          <t>6384.3116209553</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-67.34</t>
+          <t>6664.35606501167</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-65.75</t>
+          <t>7593.47009763796</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-62.62</t>
+          <t>9632.78411611902</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-62.56</t>
+          <t>11415.8392821631</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-62.71</t>
+          <t>8671.10649166191</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2527.878</t>
+          <t>1213982195.32434</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2532.762</t>
+          <t>1297409616.45887</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2500.39</t>
+          <t>1096640541.64088</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2584.313</t>
+          <t>1243645779.83752</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2724.939</t>
+          <t>1535225179.87537</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2939.244</t>
+          <t>1700780768.90202</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3091.703</t>
+          <t>1937469157.60932</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3118.961</t>
+          <t>1932968032.94763</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2910.489</t>
+          <t>1904285647.92596</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3096.281</t>
+          <t>1933582838.51839</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3080.931</t>
+          <t>1671592934.0709</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3135.15</t>
+          <t>1784785755.63979</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3134.917</t>
+          <t>1767535497.26074</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3091.074</t>
+          <t>2265114762.0354</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3082.643</t>
+          <t>1530096642.60339</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1460.903</t>
+          <t>-1917.06387778747</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1482.407</t>
+          <t>-2075.28111869819</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1478.152</t>
+          <t>-1955.41136414335</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1534.288</t>
+          <t>-1951.05495490776</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1633.083</t>
+          <t>-1929.96711645797</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1758.976</t>
+          <t>-2094.97611097832</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1844.687</t>
+          <t>-2111.42591321631</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1893.952</t>
+          <t>-2436.01910710905</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1775.693</t>
+          <t>-2743.19274726135</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1880.914</t>
+          <t>-3036.7274816556</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1882.883</t>
+          <t>-3214.26569596877</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1958.301</t>
+          <t>-3796.70043404992</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1974.027</t>
+          <t>-5021.20521398334</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2016.937</t>
+          <t>-6268.4083573104</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2035.683</t>
+          <t>-4042.61140086197</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1987.551</t>
+          <t>-794955520.390517</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2081.173</t>
+          <t>-841301796.495814</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1900.169</t>
+          <t>-678501121.788844</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1975.928</t>
+          <t>-819204769.721597</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2198.759</t>
+          <t>-1051054435.65055</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2314.637</t>
+          <t>-1157729141.94217</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2510.471</t>
+          <t>-1340487144.86157</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2586.655</t>
+          <t>-1359177277.03723</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2461.263</t>
+          <t>-1360113843.7307</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2449.79</t>
+          <t>-1447692566.92601</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2197.319</t>
+          <t>-1334715607.48413</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2198.02</t>
+          <t>-1388777122.68888</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2099.163</t>
+          <t>-1339869603.95118</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2595.129</t>
+          <t>-1808609090.96238</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1879.506</t>
+          <t>-1233450350.21325</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3289.33855</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3301.17601</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3070.01195</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3277.96135</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3227.9768</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2970.60471</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3048.41562</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3366.44822</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>4252.8315</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>4995.28712</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5266.43538</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5524.38471</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>6331.55874</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>7278.69535</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>6796.58128</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1041.998</t>
+          <t>0.0375187785128083</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1021.044</t>
+          <t>0.0341515113624229</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1000.045</t>
+          <t>0.032030009690466</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1019.057</t>
+          <t>0.0388912941557167</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1040.734</t>
+          <t>0.0431555061880204</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1114.238</t>
+          <t>0.0443602917796223</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1146.978</t>
+          <t>0.0461548987236938</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1144.392</t>
+          <t>0.0352635423620661</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1071.983</t>
+          <t>0.0324377934266696</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1113.225</t>
+          <t>0.035519351409085</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1101.804</t>
+          <t>0.0367211643522404</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1099.722</t>
+          <t>0.0362572743582257</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1110.986</t>
+          <t>0.0419947262059996</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1056.494</t>
+          <t>0.0388144924550873</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1061.376</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4009.30204461226</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4110.62893189141</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3985.18004554325</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4160.21885548685</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4226.76494684178</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3977.86902232336</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4095.1821265542</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4664.52482765077</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6094.95444184257</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>7135.12399070072</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>7639.76272830467</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>8245.92046224411</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>9545.39955151358</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>11024.2451353322</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>10604.365021569</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1379.668</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1380.545</t>
+          <t>5428.85074392709</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1376.116</t>
+          <t>5270.72917188927</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1524.836</t>
+          <t>5483.52170324111</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1534.477</t>
+          <t>5598.45614178127</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1511.117</t>
+          <t>5290.57706587232</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1600.865</t>
+          <t>5477.72397844922</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1776.704</t>
+          <t>6144.2804408705</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2014.68</t>
+          <t>8016.30446858495</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2276.546</t>
+          <t>9440.96012703077</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2265.995</t>
+          <t>10170.0773856905</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2269.966</t>
+          <t>10905.9669471042</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2211.777</t>
+          <t>12486.3005746237</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2265.157</t>
+          <t>14467.4037383969</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2302.876</t>
+          <t>13817.1416338568</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>36529.8037857805</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>37487.7032509869</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>35563.213394576</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>36751.9667967827</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>36265.9523848064</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>32633.2348156165</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>33016.6545840697</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>36533.9452894855</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>45002.8512596556</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>53359.7893934907</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>57946.9071727335</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-13.73</t>
+          <t>62627.0932247143</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>72474.0691091171</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>86099.5392394877</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.961</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6.983</t>
+          <t>5455.39135868644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>5645.12988085847</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6.981</t>
+          <t>5745.15417948743</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8.075</t>
+          <t>6005.84982413465</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8.596</t>
+          <t>6349.97905401159</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6647.25188224167</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>7.891</t>
+          <t>7098.23950453184</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6.215</t>
+          <t>7575.489937585</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5.675</t>
+          <t>8045.80011186733</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8497.11821011226</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.108</t>
+          <t>8705.03496547207</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.311</t>
+          <t>8949.51823133714</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.439</t>
+          <t>9176.45124006597</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.629</t>
+          <t>9087.11431011384</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4009.30204461226</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4126.86311251552</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4270.32832980622</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4369.6860878491</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4512.5640103078</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4742.11401089715</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4921.84600579111</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5363.73180868011</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5738.08342482409</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6066.29332678926</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6391.84905601753</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6596.88058665277</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6858.45153611619</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7047.65434601301</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7008.56538602621</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3172.16004244469</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3165.50374607291</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2982.04383811073</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3424.83096675889</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3538.95208821873</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3332.77408412768</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3426.66917155078</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3506.5505591295</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4036.85876141505</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4834.98669296923</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5117.16685430948</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5605.02821289582</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>6906.09197537635</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>8015.98120160314</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>7436.5410161432</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1460902785.11247</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1482406531.00876</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1478152424.3377</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1534288491.79434</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1633082847.97895</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1758975797.03712</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1844686572.44164</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1893952098.86209</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1775692821.52584</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1880914389.42031</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1882882689.5124</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1958301143.90031</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1974026520.50223</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2016937073.30633</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2035682517.27597</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2527877714.48903</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2532761931.56296</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2500390406.00606</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2584313293.44543</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2724938995.28021</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2939243585.06821</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3091703440.77829</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3118961336.08756</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2910488611.39803</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3096281280.00308</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3080931278.59047</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3135150451.41462</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3134916930.77745</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3091073516.42186</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3082642951.65963</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1041997520.93818</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1021044338.09878</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1000045247.41479</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1019056626.78826</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1040734261.82765</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1114237619.09915</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1146977766.10291</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1144392339.37645</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1071983320.00049</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1113225252.04762</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1101804241.44741</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1099721648.53697</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1110986466.17874</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1056494488.23706</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1061375713.43295</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>297700</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>299500</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>304100</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>309800</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>314800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>321900</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>328300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>340800</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>353300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>366400</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>372400</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>384500</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>391166.670871672</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>392612.725033373</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>223716.495232719</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>225937.149256762</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>228763.11685584</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>233286.523036485</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>237983.052303308</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>241700</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>248200</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>255600</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>262900</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>273900</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>285800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>308800</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>326600</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>325400</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>556844000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>559558000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>565864000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>576508000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>590902000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>605960000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>626986000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>631030000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>652422000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>663882000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>679879000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>694745000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>715064000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>724744333.122296</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>725571484.03977</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>385081830.189556</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>388735218.183415</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>393173063.331875</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>400650693.290692</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>410295651.543646</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>421155000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>433872000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>443031000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>455955000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>458638000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>473113000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>494479000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>516413000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>540570000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>541705000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.390116927880701</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.384904366830866</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.369970763777891</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.352881576519591</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.353397642917275</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.358280413431593</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.353910440875485</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.358248084348114</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.339631106733564</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.364859725162261</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.347331262498627</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.353356172580841</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.36971202850082</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.361581828929178</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.361957673459242</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.321293200762932</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.328626938735117</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.322348896331952</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.315242186789605</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.337233876652075</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.342979664793355</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.349594082475155</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.348925892107897</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.338509157324964</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.365575717545096</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.379463226115965</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.387763044649832</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.383128728066806</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.395468700852395</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.399773244605587</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.288589871356368</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.286468694434018</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.307680339890158</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.331876236690805</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.30936848043065</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.298739921775052</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.296495476649359</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.292826023543989</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.321859735941472</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.269564557292643</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.273205511385408</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.258880782769327</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.247159243432374</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.242949470218427</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.238269081935171</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.534188139336053</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.532011315873177</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.523302522577204</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.517250438282201</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.511809080747415</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.523897577386329</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.528373940845939</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.538035222905255</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.534350545187074</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.527190060394804</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.506043879902198</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.502750800440531</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.519150926758474</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.52249179233009</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.532869140480181</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.348159438487842</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.350791303722316</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.348628315544066</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.346776855493985</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.367228702692849</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.365108731851971</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.36395074825005</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.356912062558847</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.358449735647864</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.373252046723813</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.392121724222384</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.398425952750391</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.382822896476434</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.383175701757355</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.377118085097003</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.117652422176104</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.117197380404507</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.12806916187873</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.135972706223814</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.120962216559736</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.1109936907617</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.107675310904011</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.105052714535898</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.107199719165062</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0995578928813832</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.101834395875418</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0988232468090778</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0980261767650918</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0943325059125545</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0900127744228161</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13745.56817</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14025.103</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>13541.08615</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>14456.44642</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>14904.16569</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>14176.64369</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14825.93409</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>16295.25573</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20252.26861</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>23628.63618</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>25577.21377</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>28109.62515</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>33700.83554</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>40127.54318</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>37463.21071</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>8457.07898</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8594.35449</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8252.77301</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8908.35267</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9137.40823</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8623.35115</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8904.39315</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9650.831</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>12053.16323</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>14275.94682</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>15287.24424</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>16510.99516</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>19392.39255</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>22483.38494</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>21253.68265</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>28225.7804786168</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28703.0313879198</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29087.669044844</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>29535.6804326495</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>29943.9567213731</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>30381.0747399953</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30840.3990575789</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>31403.4282774735</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>31951.0194714376</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>32656.6168437408</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33395.9865417147</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>34307.1617116782</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>35470.9755419079</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>36716.5888590675</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
